--- a/data/GWAS/GLM_sig_markers_Stem_Length_protein_function_candidate.xlsx
+++ b/data/GWAS/GLM_sig_markers_Stem_Length_protein_function_candidate.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/wen-hsi_kuo_wustl_edu/Documents/MOBOT/MOBOT_Boltonia/data/GWAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_AE7DFDCE8F79A8D366075C52F33D0231778FBE8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C52607-514B-CB4E-8057-F44497B09923}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_AE7DFDCE8F79A8D366075C52F33D0231778FBE8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DAE792-9905-654F-B613-D3A5E83EFA31}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="37360" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="37360" windowHeight="16240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
   <si>
     <t>qseqid</t>
   </si>
@@ -182,13 +183,28 @@
   </si>
   <si>
     <t>Kinesin-like protein; cytoskeleton/organelle dynamics may impact cell elongation and organ growth, though mechanism is less specific than AHA9/DXS2.</t>
+  </si>
+  <si>
+    <t>Gene_ID</t>
+  </si>
+  <si>
+    <t>Gene_Symbol</t>
+  </si>
+  <si>
+    <t>Protein_Name</t>
+  </si>
+  <si>
+    <t>Uniprot_Accession</t>
+  </si>
+  <si>
+    <t>Potential_Function</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +220,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -213,7 +235,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -236,11 +258,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -258,6 +291,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -825,4 +861,140 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290275E4-B93D-244E-BDE6-995B5512ED72}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.1640625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>